--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case MedicationRequest, Variation VA Order</t>
+    <t>This StructureDefinition contains the maps for VistA ORDER (file 100) to FHIR MedicationRequest</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4619" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4619" uniqueCount="790">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -252,10 +252,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Prescription
@@ -675,10 +675,10 @@
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
+    <t>1238: source value from ORDER - DC REASON TEXT (#100-65)</t>
+  </si>
+  <si>
     <t>CPRSOrder.CPRSOrder.DiscontinuedOrderReasonText</t>
-  </si>
-  <si>
-    <t>1238: source value from ORDER - DC REASON TEXT (#100-65)</t>
   </si>
   <si>
     <t>MedicationRequest.intent</t>
@@ -703,6 +703,10 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-11:1346: fixed value "order" {null}inv-12:1540: fixed value "plan" {null}</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -747,10 +751,10 @@
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
   </si>
   <si>
+    <t>1233: terminologyMaps using null on ORDER - PATIENT CLASS (#100-10)</t>
+  </si>
+  <si>
     <t>CPRSOrder.CPRSOrder.InPatientFlag</t>
-  </si>
-  <si>
-    <t>1233: terminologyMaps using null on ORDER - PATIENT CLASS (#100-10)</t>
   </si>
   <si>
     <t>MedicationRequest.category:us-core</t>
@@ -829,6 +833,10 @@
   </si>
   <si>
     <t>reportedBoolean</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-13:1347: fixed value "true" {null}</t>
   </si>
   <si>
     <t>1347: fixed value = true if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>
@@ -883,11 +891,11 @@
     <t>medicationCodeableConcept</t>
   </si>
   <si>
+    <t>1549: source value from ORDER - ITEM ORDERED (#100-7)</t>
+  </si>
+  <si>
     <t>CPRSOrder.CPRSOrder.ItemOrderedParentFileIEN
 CPRSOrder.CPRSOrder.ItemOrderedParentFileNumber</t>
-  </si>
-  <si>
-    <t>1549: source value from ORDER - ITEM ORDERED (#100-7)</t>
   </si>
   <si>
     <t>MedicationRequest.subject</t>
@@ -923,14 +931,14 @@
     <t>PID-3-Patient ID List</t>
   </si>
   <si>
+    <t>1226: reference from ORDER - OBJECT OF ORDER (#100-.02)</t>
+  </si>
+  <si>
     <t>CPRSOrder.OrderAction.ObjectOfOrderIEN
 CPRSOrder.OrderAction.ObjectOfOrderPatientIEN
 CPRSOrder.OrderAction.ParentFileNumber</t>
   </si>
   <si>
-    <t>1226: reference from ORDER - OBJECT OF ORDER (#100-.02)</t>
-  </si>
-  <si>
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
@@ -1004,6 +1012,9 @@
   </si>
   <si>
     <t>RXE-32-Original Order Date/Time / ORC-9-Date/Time of Transaction</t>
+  </si>
+  <si>
+    <t>1228: source value from ORDER - WHEN ENTERED (#100-4)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.EnteredDateTime
@@ -1012,9 +1023,6 @@
 CPRSOrder.OrderedItem.EnteredVistaDate</t>
   </si>
   <si>
-    <t>1228: source value from ORDER - WHEN ENTERED (#100-4)</t>
-  </si>
-  <si>
     <t>MedicationRequest.requester</t>
   </si>
   <si>
@@ -1562,6 +1570,9 @@
   </si>
   <si>
     <t>DR.1</t>
+  </si>
+  <si>
+    <t>1234: source value from ORDER - START DATE (#100-21)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.OrderStartDateTime
@@ -1571,9 +1582,6 @@
 CPRSOrder.OrderedItem.OrderStartVistaDate</t>
   </si>
   <si>
-    <t>1234: source value from ORDER - START DATE (#100-21)</t>
-  </si>
-  <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.bounds[x]:boundsPeriod.end</t>
   </si>
   <si>
@@ -1599,15 +1607,15 @@
   </si>
   <si>
     <t>DR.2</t>
+  </si>
+  <si>
+    <t>1235: source value from ORDER - STOP DATE (#100-22)</t>
   </si>
   <si>
     <t>CPRSOrder.CPRSOrder.OrderStopDateTime
 CPRSOrder.CPRSOrder.OrderStopVistaDate
 CPRSOrder.OrderedItem.OrderStopDateTime
 CPRSOrder.OrderedItem.OrderStopVistaDate</t>
-  </si>
-  <si>
-    <t>1235: source value from ORDER - STOP DATE (#100-22)</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction.timing.repeat.count</t>
@@ -2834,8 +2842,8 @@
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="50.60546875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="101.44921875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="101.44921875" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="50.60546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4193,10 +4201,10 @@
         <v>158</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="AQ11" t="s" s="2">
-        <v>159</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -4316,10 +4324,10 @@
         <v>83</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="AQ12" t="s" s="2">
-        <v>171</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
@@ -4439,10 +4447,10 @@
         <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="AQ13" t="s" s="2">
-        <v>182</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -5038,36 +5046,36 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>223</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5093,13 +5101,13 @@
         <v>173</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -5128,16 +5136,16 @@
         <v>177</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
@@ -5147,7 +5155,7 @@
         <v>193</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -5165,33 +5173,33 @@
         <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -5216,13 +5224,13 @@
         <v>173</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -5251,10 +5259,10 @@
         <v>164</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>83</v>
@@ -5272,7 +5280,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -5290,13 +5298,13 @@
         <v>83</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -5310,10 +5318,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5339,10 +5347,10 @@
         <v>112</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5372,10 +5380,10 @@
         <v>164</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -5393,7 +5401,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5408,16 +5416,16 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -5431,10 +5439,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5457,16 +5465,16 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5516,7 +5524,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5537,7 +5545,7 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>83</v>
@@ -5554,10 +5562,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5580,13 +5588,13 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5625,7 +5633,7 @@
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5635,7 +5643,7 @@
         <v>193</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5656,7 +5664,7 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>83</v>
@@ -5673,13 +5681,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>83</v>
@@ -5701,13 +5709,13 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5758,7 +5766,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5770,7 +5778,7 @@
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -5779,7 +5787,7 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>83</v>
@@ -5788,18 +5796,18 @@
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>260</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5822,16 +5830,16 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5857,17 +5865,17 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5877,7 +5885,7 @@
         <v>193</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>92</v>
@@ -5892,19 +5900,19 @@
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5915,13 +5923,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>83</v>
@@ -5946,13 +5954,13 @@
         <v>173</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5978,11 +5986,11 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -6000,7 +6008,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -6015,33 +6023,33 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6064,16 +6072,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -6123,7 +6131,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>92</v>
@@ -6138,33 +6146,33 @@
         <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6187,16 +6195,16 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6246,7 +6254,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -6261,19 +6269,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -6284,10 +6292,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6310,13 +6318,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6367,7 +6375,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6382,16 +6390,16 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -6405,10 +6413,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6431,13 +6439,13 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6488,7 +6496,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6503,33 +6511,33 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6552,13 +6560,13 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6609,7 +6617,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6624,33 +6632,33 @@
         <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6673,13 +6681,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6730,7 +6738,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6745,16 +6753,16 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6768,10 +6776,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6797,13 +6805,13 @@
         <v>173</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6832,10 +6840,10 @@
         <v>177</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6853,7 +6861,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6868,13 +6876,13 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
@@ -6891,10 +6899,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6917,13 +6925,13 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6974,7 +6982,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6995,10 +7003,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -7012,10 +7020,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7041,13 +7049,13 @@
         <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -7076,10 +7084,10 @@
         <v>177</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -7097,7 +7105,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -7112,19 +7120,19 @@
         <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -7135,10 +7143,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7161,16 +7169,16 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7220,7 +7228,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7235,16 +7243,16 @@
         <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>168</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -7258,10 +7266,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7284,13 +7292,13 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7341,7 +7349,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7356,13 +7364,13 @@
         <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
@@ -7379,10 +7387,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7408,10 +7416,10 @@
         <v>106</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7462,7 +7470,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7483,7 +7491,7 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>83</v>
@@ -7500,10 +7508,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7526,13 +7534,13 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7583,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7598,13 +7606,13 @@
         <v>104</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
@@ -7621,10 +7629,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7650,14 +7658,14 @@
         <v>150</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7706,7 +7714,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7721,13 +7729,13 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
@@ -7744,10 +7752,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7773,13 +7781,13 @@
         <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7808,10 +7816,10 @@
         <v>177</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7829,7 +7837,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7850,7 +7858,7 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>83</v>
@@ -7867,10 +7875,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7893,13 +7901,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7950,7 +7958,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7965,13 +7973,13 @@
         <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -7988,10 +7996,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8014,13 +8022,13 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -8071,7 +8079,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -8086,13 +8094,13 @@
         <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -8109,10 +8117,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8135,16 +8143,16 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8194,7 +8202,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -8209,13 +8217,13 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -8232,10 +8240,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8353,10 +8361,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8476,14 +8484,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8505,10 +8513,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -8563,7 +8571,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8601,10 +8609,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8627,17 +8635,17 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8686,7 +8694,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8707,13 +8715,13 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -8724,10 +8732,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8753,14 +8761,14 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8809,7 +8817,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8830,13 +8838,13 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -8847,10 +8855,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8876,16 +8884,16 @@
         <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8913,10 +8921,10 @@
         <v>177</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8934,7 +8942,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8955,13 +8963,13 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8972,10 +8980,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9001,10 +9009,10 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -9055,7 +9063,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9076,13 +9084,13 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -9093,10 +9101,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9119,19 +9127,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -9180,7 +9188,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9201,7 +9209,7 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
@@ -9218,10 +9226,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9339,10 +9347,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9462,14 +9470,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9491,10 +9499,10 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -9549,7 +9557,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9587,10 +9595,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9613,17 +9621,17 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9672,7 +9680,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9693,7 +9701,7 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>83</v>
@@ -9710,10 +9718,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9736,17 +9744,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9795,7 +9803,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9807,7 +9815,7 @@
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -9816,7 +9824,7 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
@@ -9833,10 +9841,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9954,10 +9962,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10077,10 +10085,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10103,13 +10111,13 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10148,7 +10156,7 @@
         <v>83</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -10158,7 +10166,7 @@
         <v>193</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10179,7 +10187,7 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
@@ -10196,13 +10204,13 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>83</v>
@@ -10224,13 +10232,13 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10281,7 +10289,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10302,7 +10310,7 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
@@ -10319,10 +10327,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10440,10 +10448,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10563,10 +10571,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10589,16 +10597,16 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10648,7 +10656,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10657,7 +10665,7 @@
         <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>104</v>
@@ -10669,27 +10677,27 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10712,23 +10720,23 @@
         <v>93</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q65" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>83</v>
@@ -10773,7 +10781,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10782,7 +10790,7 @@
         <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>104</v>
@@ -10794,27 +10802,27 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10837,19 +10845,19 @@
         <v>93</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10898,7 +10906,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10919,7 +10927,7 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>83</v>
@@ -10936,10 +10944,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10962,13 +10970,13 @@
         <v>93</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11019,7 +11027,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11040,7 +11048,7 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>83</v>
@@ -11057,10 +11065,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11083,19 +11091,19 @@
         <v>93</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -11144,7 +11152,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11165,7 +11173,7 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>83</v>
@@ -11182,10 +11190,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11208,19 +11216,19 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -11269,7 +11277,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11290,7 +11298,7 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>83</v>
@@ -11307,10 +11315,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11336,10 +11344,10 @@
         <v>112</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11369,10 +11377,10 @@
         <v>164</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -11390,7 +11398,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11411,7 +11419,7 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>83</v>
@@ -11428,10 +11436,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11454,13 +11462,13 @@
         <v>93</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11468,7 +11476,7 @@
         <v>83</v>
       </c>
       <c r="Q71" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>83</v>
@@ -11513,7 +11521,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11534,7 +11542,7 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>83</v>
@@ -11551,10 +11559,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11577,13 +11585,13 @@
         <v>93</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11634,7 +11642,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11655,7 +11663,7 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>83</v>
@@ -11672,10 +11680,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11698,13 +11706,13 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11755,7 +11763,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11776,7 +11784,7 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>83</v>
@@ -11793,10 +11801,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11819,13 +11827,13 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11876,7 +11884,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11897,7 +11905,7 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>83</v>
@@ -11914,10 +11922,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11943,10 +11951,10 @@
         <v>112</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11976,10 +11984,10 @@
         <v>164</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11997,7 +12005,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12018,7 +12026,7 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>83</v>
@@ -12035,10 +12043,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12064,13 +12072,13 @@
         <v>112</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12100,7 +12108,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -12118,7 +12126,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12156,10 +12164,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12182,16 +12190,16 @@
         <v>93</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12241,7 +12249,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12279,10 +12287,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12308,16 +12316,16 @@
         <v>112</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12345,10 +12353,10 @@
         <v>164</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -12366,7 +12374,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12387,7 +12395,7 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>83</v>
@@ -12404,10 +12412,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12430,13 +12438,13 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12487,7 +12495,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12508,7 +12516,7 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>83</v>
@@ -12525,10 +12533,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12554,13 +12562,13 @@
         <v>173</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12589,10 +12597,10 @@
         <v>116</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12610,7 +12618,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12631,7 +12639,7 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>83</v>
@@ -12648,10 +12656,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12674,16 +12682,16 @@
         <v>93</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12712,10 +12720,10 @@
         <v>177</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12733,7 +12741,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12754,13 +12762,13 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12771,10 +12779,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12800,16 +12808,16 @@
         <v>173</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12837,10 +12845,10 @@
         <v>177</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12858,7 +12866,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12879,13 +12887,13 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12896,10 +12904,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12925,14 +12933,14 @@
         <v>173</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12960,10 +12968,10 @@
         <v>177</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12981,7 +12989,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13002,13 +13010,13 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -13019,10 +13027,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13048,16 +13056,16 @@
         <v>173</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -13085,10 +13093,10 @@
         <v>177</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -13106,7 +13114,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13127,13 +13135,13 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -13144,10 +13152,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13170,13 +13178,13 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13227,7 +13235,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13254,7 +13262,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13265,10 +13273,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13386,10 +13394,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13509,10 +13517,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13538,14 +13546,14 @@
         <v>173</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13573,10 +13581,10 @@
         <v>177</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>83</v>
@@ -13594,7 +13602,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13621,7 +13629,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13632,10 +13640,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13658,19 +13666,19 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13719,7 +13727,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13740,13 +13748,13 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13757,10 +13765,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13783,19 +13791,19 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13844,7 +13852,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13865,13 +13873,13 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13882,10 +13890,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13908,19 +13916,19 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13969,7 +13977,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13990,13 +13998,13 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -14007,10 +14015,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14033,19 +14041,19 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -14094,7 +14102,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -14115,7 +14123,7 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>83</v>
@@ -14132,10 +14140,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14158,17 +14166,17 @@
         <v>93</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -14217,7 +14225,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14238,7 +14246,7 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>83</v>
@@ -14255,10 +14263,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14281,13 +14289,13 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14338,7 +14346,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14356,10 +14364,10 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>83</v>
@@ -14376,10 +14384,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14497,10 +14505,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14620,14 +14628,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14649,10 +14657,10 @@
         <v>138</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>141</v>
@@ -14707,7 +14715,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14745,10 +14753,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14771,16 +14779,16 @@
         <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14830,7 +14838,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14851,7 +14859,7 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>83</v>
@@ -14868,10 +14876,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14989,10 +14997,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15112,14 +15120,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15141,10 +15149,10 @@
         <v>138</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>141</v>
@@ -15199,7 +15207,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15237,10 +15245,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15263,13 +15271,13 @@
         <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15320,7 +15328,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15341,7 +15349,7 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>83</v>
@@ -15358,10 +15366,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15384,13 +15392,13 @@
         <v>83</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15441,7 +15449,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15462,7 +15470,7 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>83</v>
@@ -15479,10 +15487,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15505,13 +15513,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15562,7 +15570,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15583,7 +15591,7 @@
         <v>83</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>83</v>
@@ -15600,10 +15608,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15626,19 +15634,19 @@
         <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15687,7 +15695,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15705,10 +15713,10 @@
         <v>83</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>83</v>
@@ -15725,10 +15733,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15751,16 +15759,16 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15810,7 +15818,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15828,16 +15836,16 @@
         <v>83</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -15848,10 +15856,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15874,13 +15882,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15931,7 +15939,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15949,16 +15957,16 @@
         <v>83</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15969,10 +15977,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15995,16 +16003,16 @@
         <v>83</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -16054,7 +16062,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16072,10 +16080,10 @@
         <v>83</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>83</v>
@@ -16092,10 +16100,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16118,13 +16126,13 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16175,7 +16183,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -16196,10 +16204,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -16213,10 +16221,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16239,13 +16247,13 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -16296,7 +16304,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16314,10 +16322,10 @@
         <v>83</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>83</v>
@@ -16334,10 +16342,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16455,10 +16463,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16578,14 +16586,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16607,10 +16615,10 @@
         <v>138</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>141</v>
@@ -16665,7 +16673,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16703,10 +16711,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16729,16 +16737,16 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16767,10 +16775,10 @@
         <v>177</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16788,7 +16796,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>92</v>
@@ -16806,16 +16814,16 @@
         <v>83</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16826,10 +16834,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16855,10 +16863,10 @@
         <v>173</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16888,10 +16896,10 @@
         <v>177</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -16909,7 +16917,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16927,16 +16935,16 @@
         <v>83</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -16947,10 +16955,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16973,13 +16981,13 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -17030,7 +17038,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17045,13 +17053,13 @@
         <v>104</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>83</v>
@@ -17060,22 +17068,22 @@
         <v>83</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>83</v>
+        <v>775</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>773</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -17094,16 +17102,16 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -17153,7 +17161,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17174,7 +17182,7 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>83</v>
@@ -17191,10 +17199,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17217,16 +17225,16 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -17276,7 +17284,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17291,13 +17299,13 @@
         <v>104</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>83</v>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -704,7 +704,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-11:1346: fixed value "order" {null}inv-12:1540: fixed value "plan" {null}</t>
+inv-17:1346: fixed value = order if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Null {null}inv-18:1540: fixed value = plan if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null {null}</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -836,7 +836,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-13:1347: fixed value "true" {null}</t>
+inv-19:1347: fixed value = true if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null {null}</t>
   </si>
   <si>
     <t>1347: fixed value = true if NON-VA MEDS - ORDER NUMBER (#55.05-7) case Not null</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
+++ b/docs/StructureDefinition-MedicationRequestVAOrder.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
